--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H943"/>
+  <dimension ref="A1:H952"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36254,6 +36254,348 @@
         <v>3</v>
       </c>
     </row>
+    <row r="944">
+      <c r="A944" t="n">
+        <v>991</v>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>TPM-0561</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>P20512-06</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H944" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="n">
+        <v>992</v>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>TPM-0561</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>PP20204-12</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H945" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="n">
+        <v>993</v>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>TPM-0561</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>PP20203-13</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H946" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="n">
+        <v>994</v>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>TPM-0562</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>P20512-07</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H947" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="n">
+        <v>995</v>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>TPM-0562</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>PP13949-04</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H948" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="n">
+        <v>996</v>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>TPM-0562</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>PP13949-09</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H949" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="n">
+        <v>997</v>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>TPM-0563</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>PP20205-121</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H950" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="n">
+        <v>998</v>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>TPM-0563</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>PP20205-061</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H951" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="n">
+        <v>999</v>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>TPM-0563</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>PP20205-131</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H952" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H952"/>
+  <dimension ref="A1:H974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36596,6 +36596,842 @@
         <v>12</v>
       </c>
     </row>
+    <row r="953">
+      <c r="A953" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>P20153S-04</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H953" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>P20321S-05</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H954" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>P20321S-06</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H955" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>12-D-6015-05</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H956" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>12-D-6017-02</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H957" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>12-6267-01</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H958" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>13-D-6195-01</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H959" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>11-A-6037-01</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H960" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>12-6265-01</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H961" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>P20321-13</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H962" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>P20321-12</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H963" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>TPM-0564</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>P20346-04</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H964" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>TPM-0565</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>12-6383-01</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H965" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="n">
+        <v>1013</v>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>TPM-0565</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>96-6183-01</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H966" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="n">
+        <v>1014</v>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>TPM-0565</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>96-6183-02</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H967" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="n">
+        <v>1015</v>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>TPM-0565</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>PP14112-19</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H968" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="n">
+        <v>1016</v>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>TPM-0566</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>PP20203-13</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H969" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="n">
+        <v>1017</v>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>TPM-0566</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>11-A-6030-01</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H970" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="n">
+        <v>1018</v>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>TPM-0566</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>P17311-17</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H971" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="n">
+        <v>1019</v>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>TPM-0566</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>P20512-06</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H972" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>TPM-0566</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>P20512-18</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H973" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>TPM-0566</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>13-D-6196-01</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H974" t="n">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H974"/>
+  <dimension ref="A1:H990"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37432,6 +37432,614 @@
         <v>26</v>
       </c>
     </row>
+    <row r="975">
+      <c r="A975" t="n">
+        <v>1022</v>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>TPM-0567</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>12-D-6234-08</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H975" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="n">
+        <v>1023</v>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>TPM-0567</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>PP20203-12</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H976" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>TPM-0567</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>12-D-6234-06</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H977" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="n">
+        <v>1025</v>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>TPM-0567</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>P20321-15-12</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H978" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="n">
+        <v>1026</v>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>TPM-0567</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>P20321-15-11</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H979" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="n">
+        <v>1027</v>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>TPM-0567</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>PP13949-08</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H980" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="n">
+        <v>1028</v>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>TPM-0567</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>PP20203-06</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H981" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="n">
+        <v>1029</v>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>TPM-0567</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>PP20204-06</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H982" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="n">
+        <v>1030</v>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>TPM-0568</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>PP20203-06</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H983" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="n">
+        <v>1031</v>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>TPM-0568</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>PP20204-13</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H984" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="n">
+        <v>1032</v>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>TPM-0568</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>P20321-21</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H985" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="n">
+        <v>1033</v>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>TPM-0568</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>P20512-18</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H986" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="n">
+        <v>1034</v>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>TPM-0568</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>12-D-6234-08</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H987" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="n">
+        <v>1035</v>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>TPM-0568</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>13-D-6196-01</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H988" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="n">
+        <v>1036</v>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>TPM-0568</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>P20512-06</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H989" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="n">
+        <v>1037</v>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>TPM-0568</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>PP13949-10</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H990" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H990"/>
+  <dimension ref="A1:H1006"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38040,6 +38040,614 @@
         <v>12</v>
       </c>
     </row>
+    <row r="991">
+      <c r="A991" t="n">
+        <v>1038</v>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>TPM-0569</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>11-A-6016-01</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H991" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="n">
+        <v>1039</v>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>TPM-0570</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>12-D-6083-05</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H992" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="n">
+        <v>1040</v>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>TPM-0571</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>12-D-6107-01</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H993" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="n">
+        <v>1041</v>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>TPM-0571</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>17-D-6047-01</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H994" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="n">
+        <v>1042</v>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>TPM-0571</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>12-D-6091-08</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H995" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="n">
+        <v>1043</v>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>TPM-0572</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>11-A-6004-01</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H996" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="n">
+        <v>1044</v>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>TPM-0572</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>11-D-3402-01</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H997" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="n">
+        <v>1045</v>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>TPM-0572</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>12-6010-04</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H998" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="n">
+        <v>1046</v>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>TPM-0572</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>12-6355-02</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H999" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="n">
+        <v>1047</v>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>TPM-0572</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>12-D-6080-06</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H1000" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="n">
+        <v>1048</v>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>TPM-0572</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>12-D-6083-03</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H1001" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="n">
+        <v>1049</v>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>TPM-0572</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>12-D-6088-06</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H1002" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>TPM-0572</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>12-D-6106-07</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H1003" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="n">
+        <v>1051</v>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>TPM-0572</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>12-D-6106-08</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H1004" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="n">
+        <v>1052</v>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>TPM-0573</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>12-D-6106-09</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H1005" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="n">
+        <v>1053</v>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>TPM-0574</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>12-D-6106-01</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>PO 2603-2838</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>Proyecto SWBD META</t>
+        </is>
+      </c>
+      <c r="H1006" t="n">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -38089,7 +38089,7 @@
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>12-D-6083-05</t>
+          <t>12-D-6091-08</t>
         </is>
       </c>
       <c r="D992" t="inlineStr">
@@ -38113,7 +38113,7 @@
         </is>
       </c>
       <c r="H992" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="993">
@@ -38583,7 +38583,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>12-D-6106-09</t>
+          <t>12-D-6106-01</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1006"/>
+  <dimension ref="A1:H1016"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38648,6 +38648,386 @@
         <v>32</v>
       </c>
     </row>
+    <row r="1007">
+      <c r="A1007" t="n">
+        <v>1054</v>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>TPM-0575</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>P20512-08</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1007" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="n">
+        <v>1055</v>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>TPM-0575</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>P20512-09</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1008" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="n">
+        <v>1056</v>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>TPM-0575</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>P20321-15-11</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1009" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="n">
+        <v>1057</v>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>TPM-0575</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>P20512-18</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1010" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="n">
+        <v>1058</v>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>TPM-0575</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>P20512-06</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1011" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="n">
+        <v>1059</v>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>TPM-0575</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>P20321-21</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1012" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="n">
+        <v>1060</v>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>TPM-0575</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>PP20204-13</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1013" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="n">
+        <v>1061</v>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>TPM-0575</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>12-D-6234-08</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1014" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="n">
+        <v>1062</v>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>TPM-0575</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>13-D-6195-01</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1015" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="n">
+        <v>1063</v>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>TPM-0575</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>PP20203-12</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1016" t="n">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1016"/>
+  <dimension ref="A1:H1017"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39028,6 +39028,44 @@
         <v>17</v>
       </c>
     </row>
+    <row r="1017">
+      <c r="A1017" t="n">
+        <v>1064</v>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>TPM-0576</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>11-A-6015-01</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>PO 2609-3836</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>INT-000</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PROYECTO LC8</t>
+        </is>
+      </c>
+      <c r="H1017" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1017"/>
+  <dimension ref="A1:H1039"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39066,6 +39066,842 @@
         <v>6</v>
       </c>
     </row>
+    <row r="1018">
+      <c r="A1018" t="n">
+        <v>1065</v>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>11-D-6165-01</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1018" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="n">
+        <v>1066</v>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>12-6267-01</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1019" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="n">
+        <v>1067</v>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>13-D-6195-01</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1020" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="n">
+        <v>1068</v>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>P20321-15-11</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1021" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="n">
+        <v>1069</v>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>P20321-21</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1022" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="n">
+        <v>1070</v>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>P20346-04</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1023" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="n">
+        <v>1071</v>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>P20512-07</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1024" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="n">
+        <v>1072</v>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>P20512-09</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1025" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="n">
+        <v>1073</v>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>P20512-18</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1026" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="n">
+        <v>1074</v>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>PP13949-04</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1027" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="n">
+        <v>1075</v>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>PP13949-08</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1028" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="n">
+        <v>1076</v>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>PP13949-09</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1029" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="n">
+        <v>1077</v>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>PP13949-10</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1030" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="n">
+        <v>1078</v>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>TPM-0577</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>PP14112-19</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1031" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="n">
+        <v>1079</v>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>TPM-0578</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>PP20203-12</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1032" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="n">
+        <v>1080</v>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>TPM-0578</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>PP20203-13</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1033" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>TPM-0578</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>PP20204-06</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1034" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="n">
+        <v>1082</v>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>TPM-0578</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>PP20204-12</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1035" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="n">
+        <v>1083</v>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>TPM-0579</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>PP20205-121</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1036" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="n">
+        <v>1084</v>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>TPM-0579</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>PP20205-131</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1037" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="n">
+        <v>1085</v>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>TPM-0579</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>PP20205-132</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1038" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="n">
+        <v>1086</v>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>TPM-0579</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>P19663-24</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>URG/GALV</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>INT-047</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>Proyecto URG/GALV</t>
+        </is>
+      </c>
+      <c r="H1039" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1039"/>
+  <dimension ref="A1:H1041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39902,6 +39902,82 @@
         <v>6</v>
       </c>
     </row>
+    <row r="1040">
+      <c r="A1040" t="n">
+        <v>1087</v>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>TPM-0580</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>P19660-14</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>PO 2609-3837</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>INT-074</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PROYECTO SWBD</t>
+        </is>
+      </c>
+      <c r="H1040" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="n">
+        <v>1088</v>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>TPM-0580</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>11-A-6014-01</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>PO 2609-3837</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>INT-074</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PROYECTO SWBD</t>
+        </is>
+      </c>
+      <c r="H1041" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -36061,7 +36061,7 @@
         </is>
       </c>
       <c r="H938" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="939">

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1041"/>
+  <dimension ref="A1:H1042"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39978,6 +39978,44 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1042">
+      <c r="A1042" t="n">
+        <v>1089</v>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>TPM-0581</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>PP13629-12</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>PNC</t>
+        </is>
+      </c>
+      <c r="H1042" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1042"/>
+  <dimension ref="A1:H1069"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40016,6 +40016,1032 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1043">
+      <c r="A1043" t="n">
+        <v>1090</v>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>11-B-9194-03</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1043" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="n">
+        <v>1091</v>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>11-B-9194-04</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1044" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="n">
+        <v>1092</v>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>11-C-9115-01</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1045" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="n">
+        <v>1093</v>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>11-C-9115-02</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1046" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="n">
+        <v>1094</v>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>11-C-9230-01</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1047" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="n">
+        <v>1095</v>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>11-C-9231-01</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1048" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="n">
+        <v>1096</v>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>11-C-9232-01</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1049" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="n">
+        <v>1097</v>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>11-C-9233-01</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1050" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="n">
+        <v>1098</v>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>11-C-9233-02</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1051" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="n">
+        <v>1099</v>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>11-C-9241-01</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1052" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>11-C-9241-02</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1053" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>11-C-9242-01</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1054" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>11-C-9242-02</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1055" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>11-C-9243-01</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1056" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>11-C-9244-01</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1057" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>11-C-9246-01</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1058" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>11-C-9247-01</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1059" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>11-C-9248-01</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1060" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>11-C-9277-02</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1061" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>11-C-9285-01</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1062" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>11-A-9951-01</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1063" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>11-B-9754-01</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1064" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>11-B-9754-02</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1065" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>11-C-9229-01</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1066" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>11-C-9284-01</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1067" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>11-C-9352-01</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1068" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>TPM-0582</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>11-C-9962-01</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO</t>
+        </is>
+      </c>
+      <c r="H1069" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1069"/>
+  <dimension ref="A1:H1077"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41042,6 +41042,310 @@
         <v>4</v>
       </c>
     </row>
+    <row r="1070">
+      <c r="A1070" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>TPM-0583</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>11-A-6014-01</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>PO 2603-2815</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>INT-029</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>PROYECTO RENO 4</t>
+        </is>
+      </c>
+      <c r="H1070" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>TPM-0583</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>12-A-6199-02</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>PO 2603-2815</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>INT-029</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>PROYECTO RENO 4</t>
+        </is>
+      </c>
+      <c r="H1071" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="n">
+        <v>1119</v>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>TPM-0583</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>12-D-6080-06</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>PO 2603-2815</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>INT-029</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>PROYECTO RENO 4</t>
+        </is>
+      </c>
+      <c r="H1072" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="n">
+        <v>1120</v>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>TPM-0583</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>12-D-6091-08</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>PO 2603-2815</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>INT-029</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>PROYECTO RENO 4</t>
+        </is>
+      </c>
+      <c r="H1073" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="n">
+        <v>1121</v>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>TPM-0583</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>12-D-6106-07</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>PO 2603-2815</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>INT-029</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>PROYECTO RENO 4</t>
+        </is>
+      </c>
+      <c r="H1074" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="n">
+        <v>1122</v>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>TPM-0583</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>12-D-6107-01</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>PO 2603-2815</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>INT-029</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>PROYECTO RENO 4</t>
+        </is>
+      </c>
+      <c r="H1075" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="n">
+        <v>1123</v>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>TPM-0583</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>P13549-16</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>PO 2603-2815</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>INT-029</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>PROYECTO RENO 4</t>
+        </is>
+      </c>
+      <c r="H1076" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="n">
+        <v>1124</v>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>TPM-0583</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>PP19152-021</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>PO 2603-2815</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>INT-029</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>PROYECTO RENO 4</t>
+        </is>
+      </c>
+      <c r="H1077" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1077"/>
+  <dimension ref="A1:H1104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41346,6 +41346,1030 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1078">
+      <c r="A1078" t="n">
+        <v>1125</v>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>11-A-9023-01</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1078" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="n">
+        <v>1126</v>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>11-A-9024-01</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1079" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="n">
+        <v>1127</v>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>11-A-9025-01</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1080" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="n">
+        <v>1128</v>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>11-A-9026-01</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1081" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="n">
+        <v>1129</v>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>11-A-9027-01</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1082" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="n">
+        <v>1130</v>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>11-A-9028-01</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1083" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="n">
+        <v>1131</v>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>11-A-9040-01</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1084" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="n">
+        <v>1132</v>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>11-A-9795-01</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1085" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="n">
+        <v>1133</v>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>11-A-9815-01</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1086" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="n">
+        <v>1134</v>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>11-A-9897-01</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1087" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="n">
+        <v>1135</v>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>11-A-9908-01</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1088" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="n">
+        <v>1136</v>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>11-A-9916-01</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1089" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="n">
+        <v>1137</v>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>11-A-9917-01</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1090" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="n">
+        <v>1138</v>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>11-A-9925-01</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1091" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="n">
+        <v>1139</v>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>11-A-9927-01</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1092" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="n">
+        <v>1140</v>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>11-B-9147-01</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1093" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="n">
+        <v>1141</v>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>11-B-9618-01</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1094" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="n">
+        <v>1142</v>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>11-B-9620-01</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1095" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="n">
+        <v>1143</v>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>11-D-9832-01</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1096" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="n">
+        <v>1144</v>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>11-E-9741-01</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr"/>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="n">
+        <v>1145</v>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>11-E-9741-04</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1098" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="n">
+        <v>1146</v>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>11-E-9742-01</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1099" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="n">
+        <v>1147</v>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>11-E-9742-04</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1100" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="n">
+        <v>1148</v>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>11-E-9839-01</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1101" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="n">
+        <v>1149</v>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>11-E-9839-04</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1102" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="n">
+        <v>1150</v>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>11-F-9005-01</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1103" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="n">
+        <v>1151</v>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>TPM-0584</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>11-F-9006-01</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1104" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -42407,7 +42407,7 @@
         </is>
       </c>
       <c r="H1105" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1106">
@@ -42445,7 +42445,7 @@
         </is>
       </c>
       <c r="H1106" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1107">
@@ -42483,7 +42483,7 @@
         </is>
       </c>
       <c r="H1107" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1108">
@@ -42521,7 +42521,7 @@
         </is>
       </c>
       <c r="H1108" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1109">

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -42483,7 +42483,7 @@
         </is>
       </c>
       <c r="H1107" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1108">

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1111"/>
+  <dimension ref="A1:H1152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42638,6 +42638,1564 @@
         <v>2</v>
       </c>
     </row>
+    <row r="1112">
+      <c r="A1112" t="n">
+        <v>1159</v>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>11-A-9012-01</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1112" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="n">
+        <v>1160</v>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>11-A-9029-01</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1113" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="n">
+        <v>1161</v>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>11-A-9030-01</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1114" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="n">
+        <v>1162</v>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>11-A-9030-02</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1115" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="n">
+        <v>1163</v>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>11-A-9577-01</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1116" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="n">
+        <v>1164</v>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>11-A-9581-01</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1117" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="n">
+        <v>1165</v>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>11-A-9794-01</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1118" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="n">
+        <v>1166</v>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>11-A-9816-01</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1119" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="n">
+        <v>1167</v>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>11-A-9853-01</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1120" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="n">
+        <v>1168</v>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>11-A-9909-01</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1121" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="n">
+        <v>1169</v>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>11-A-9926-01</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1122" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="n">
+        <v>1170</v>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>11-B-9074-01</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1123" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>11-B-9079-01</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1124" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>11-B-9088-01</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1125" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>11-B-9126-01</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1126" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>11-B-9362-01</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1127" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>11-B-9411-01</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1128" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="n">
+        <v>1176</v>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>11-B-9528-01</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1129" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="n">
+        <v>1177</v>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>11-B-9697-01</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1130" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="n">
+        <v>1178</v>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>11-B-9755-01</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1131" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="n">
+        <v>1179</v>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>11-C-9300-01</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1132" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="n">
+        <v>1180</v>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>11-C-9576-02</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="n">
+        <v>1181</v>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>11-C-9639-01</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1134" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="n">
+        <v>1182</v>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>11-C-9639-02</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1135" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="n">
+        <v>1183</v>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>11-C-9681-01</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1136" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="n">
+        <v>1184</v>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>11-C-9681-02</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1137" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="n">
+        <v>1185</v>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>11-C-9926-01</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1138" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="n">
+        <v>1186</v>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>11-C-9977-01</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1139" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="n">
+        <v>1187</v>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>11-D-9004-01</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1140" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="n">
+        <v>1188</v>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>11-E-9667-01</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1141" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="n">
+        <v>1189</v>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>11-E-9851-01</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1142" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="n">
+        <v>1190</v>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>11-E-9851-02</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1143" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="n">
+        <v>1191</v>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>TPM-0586</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>PP7114-72</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1144" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="n">
+        <v>1192</v>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>TPM-0587</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>11-E-9870-02</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1145" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="n">
+        <v>1193</v>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>TPM-0587</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>11-E-9871-02</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1146" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="n">
+        <v>1194</v>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>TPM-0587</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>11-E-9872-02</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1147" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="n">
+        <v>1195</v>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>TPM-0588</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>11-A-9923-01</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1148" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="n">
+        <v>1196</v>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>TPM-0588</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>11-C-9665-01</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1149" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="n">
+        <v>1197</v>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>TPM-0588</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>11-C-9666-01</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1150" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="n">
+        <v>1198</v>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>TPM-0589</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>11-C-9669-01</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1151" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="n">
+        <v>1199</v>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>TPM-0589</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>11-E-9665-01</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1152" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1152"/>
+  <dimension ref="A1:H1155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44196,6 +44196,120 @@
         <v>2</v>
       </c>
     </row>
+    <row r="1153">
+      <c r="A1153" t="n">
+        <v>1200</v>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>TPM-0590</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>12-D-6030-07</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>PO-RUGENCIA</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>INT-000</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>Proyecto TAPAS GAL</t>
+        </is>
+      </c>
+      <c r="H1153" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>TPM-0591</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>12-D-6030-08</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>PO-RUGENCIA</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>INT-000</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>Proyecto TAPAS GAL</t>
+        </is>
+      </c>
+      <c r="H1154" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>TPM-0592</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>12-D-6030-10</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>PO-RUGENCIA</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>INT-000</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>Proyecto TAPAS GAL</t>
+        </is>
+      </c>
+      <c r="H1155" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1155"/>
+  <dimension ref="A1:H1182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44310,6 +44310,1032 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1156">
+      <c r="A1156" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>TPM-0593</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>12-D-6107-01</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1156" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>TPM-0594</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>12-D-6091-08</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>INT-004</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1157" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>TPM-0595</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>12-D-6091-07</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>INT-005</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1158" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="n">
+        <v>1206</v>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>TPM-0595</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>P19504-09</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>INT-006</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1159" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>TPM-0595</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>PP7533-05</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>INT-007</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1160" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="n">
+        <v>1208</v>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>TPM-0596</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>12-D-6107-01</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>INT-008</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1161" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="n">
+        <v>1209</v>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>TPM-0596</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>P6298-051</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>INT-009</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1162" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>TPM-0597</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>12-D-6106-07</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>INT-010</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1163" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="n">
+        <v>1211</v>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>TPM-0598</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>12-D-6106-08</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>INT-011</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1164" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>TPM-0599</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>P6298-051</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>INT-012</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1165" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="n">
+        <v>1213</v>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>TPM-0599</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>12-D-6091-08</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>INT-013</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1166" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="n">
+        <v>1214</v>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>TPM-0600</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>12-D-6091-08</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>INT-014</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1167" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>TPM-0601</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>12-D-6107-01</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>INT-015</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1168" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>TPM-0602</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>12-D-6107-01</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>INT-016</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1169" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>TPM-0603</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>12-D-6106-08</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>INT-017</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1170" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>TPM-0604</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>P6298-051</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>INT-018</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1171" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>TPM-0605</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>12-D-6107-01</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>INT-019</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1172" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>TPM-0606</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>P6298-051</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>INT-020</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1173" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>TPM-0607</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>12-D-6091-08</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>INT-021</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1174" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="n">
+        <v>1222</v>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>TPM-0608</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>P6298-051</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>INT-022</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1175" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>TPM-0609</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>12-D-6091-08</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>INT-023</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1176" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>TPM-0610</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>P6298-051</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>INT-024</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1177" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>TPM-0611</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>P6298-051</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>INT-025</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1178" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="n">
+        <v>1226</v>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>TPM-0612</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>12-D-6091-08</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>INT-026</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1179" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="n">
+        <v>1227</v>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>TPM-0613</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>12-D-6107-01</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>INT-027</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1180" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="n">
+        <v>1228</v>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>TPM-0614</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>12-D-6107-01</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>INT-028</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1181" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="n">
+        <v>1229</v>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>TPM-0615</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>12-D-6107-01</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>INT-029</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1182" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1182"/>
+  <dimension ref="A1:H1223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45336,6 +45336,1564 @@
         <v>15</v>
       </c>
     </row>
+    <row r="1183">
+      <c r="A1183" t="n">
+        <v>1230</v>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>11-E-9892-03</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1183" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="n">
+        <v>1231</v>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>11-E-9900-01</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1184" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="n">
+        <v>1232</v>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>11-E-9900-03</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1185" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="n">
+        <v>1233</v>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>11-E-9893-03</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1186" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="n">
+        <v>1234</v>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>11-E-9893-01</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1187" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="n">
+        <v>1235</v>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>11-E-9900-09</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1188" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="n">
+        <v>1236</v>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>11-C-9747-01</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1189" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="n">
+        <v>1237</v>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>11-C-9746-01</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1190" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="n">
+        <v>1238</v>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>11-E-9902-01</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1191" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="n">
+        <v>1239</v>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>11-E-9892-01</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1192" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="n">
+        <v>1240</v>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>11-E-9895-01</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1193" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="n">
+        <v>1241</v>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>11-E-9896-01</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1194" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="n">
+        <v>1242</v>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>11-E-9246-01</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1195" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="n">
+        <v>1243</v>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>TPM-0616</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>11-E-9256-01</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1196" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="n">
+        <v>1244</v>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>TPM-0617</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>11-E-9250-01</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1197" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="n">
+        <v>1245</v>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>TPM-0617</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>11-C-9611-01</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1198" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="n">
+        <v>1246</v>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>TPM-0617</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>11-C-9612-01</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1199" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="n">
+        <v>1247</v>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>TPM-0617</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>PP21139-092 TRTO</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1200" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="n">
+        <v>1248</v>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>TPM-0617</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>11-E-9909-02</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1201" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="n">
+        <v>1249</v>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>TPM-0618</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>P9711-081 TRTO 2</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="n">
+        <v>1250</v>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>TPM-0618</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>P7911-081 TRTO 1</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1203" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="n">
+        <v>1251</v>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>TPM-0618</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>PP8655 TRTO-1</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1204" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="n">
+        <v>1252</v>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>TPM-0618</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>PP8655</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1205" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="n">
+        <v>1253</v>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>TPM-0618</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>11-C-9280-01</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1206" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="n">
+        <v>1254</v>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>TPM-0618</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>P9711-081</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1207" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="n">
+        <v>1255</v>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>TPM-0618</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>P9711-081 TRTO</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1208" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="n">
+        <v>1256</v>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>TPM-0618</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>PP21139-081 TRTO</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1209" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="n">
+        <v>1257</v>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>TPM-0618</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>11-C-9778-01 TRTO</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1210" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="n">
+        <v>1258</v>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>TPM-0619</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>11-B-9195-01</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1211" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="n">
+        <v>1259</v>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>TPM-0619</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>11-E-9903-01</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1212" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="n">
+        <v>1260</v>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>TPM-0619</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>11-E-9901-01</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1213" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="n">
+        <v>1261</v>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>TPM-0620</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>11-E-9770-02 TRTO</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1214" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="n">
+        <v>1262</v>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>TPM-0620</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>11-B-9085-01</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1215" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="n">
+        <v>1263</v>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>TPM-0620</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>11-B-9374-01</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1216" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="n">
+        <v>1264</v>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>TPM-0620</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>11-A-9895-01</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1217" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="n">
+        <v>1265</v>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>TPM-0620</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>11-A-9983-01</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1218" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="n">
+        <v>1266</v>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>TPM-0620</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>11-A-9581-01 TRTO</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1219" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="n">
+        <v>1267</v>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>TPM-0620</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>11-C-9634-01</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1220" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="n">
+        <v>1268</v>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>TPM-0620</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>11-D-9643-02</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1221" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="n">
+        <v>1269</v>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>TPM-0620</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>11-D-9643-01</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1222" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="n">
+        <v>1270</v>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>TPM-0620</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>11-A-9029-02</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>PO 2609-3549</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>INT-065</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO GALV</t>
+        </is>
+      </c>
+      <c r="H1223" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1223"/>
+  <dimension ref="A1:H1224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46894,6 +46894,44 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1224">
+      <c r="A1224" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>TPM-0621</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>P20325-23</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>PO 2610-4061</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>INT-077</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>Proyecto LC8</t>
+        </is>
+      </c>
+      <c r="H1224" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1224"/>
+  <dimension ref="A1:H1259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46932,6 +46932,1336 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1225">
+      <c r="A1225" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>TPM-0622</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>12-D-6091-06</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1225" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>TPM-0623</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>12-D-6091-06</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1226" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>TPM-0624</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>12-D-6108-01</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1227" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="n">
+        <v>1275</v>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>TPM-0624</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>12-D-6099-13</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1228" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>TPM-0625</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>PP10315-01</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1229" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>TPM-0626</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>17-D-6007-01</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1230" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="n">
+        <v>1278</v>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>TPM-0627</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>12-D-6081-06</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>P0-2603-2838</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>Proyecto META</t>
+        </is>
+      </c>
+      <c r="H1231" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="n">
+        <v>1279</v>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>TPM-0627</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>12-D-6047-03</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>P0-2603-2838</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>Proyecto META</t>
+        </is>
+      </c>
+      <c r="H1232" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="n">
+        <v>1280</v>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>TPM-0627</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>12-D-6088-08</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>P0-2603-2838</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>Proyecto META</t>
+        </is>
+      </c>
+      <c r="H1233" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="n">
+        <v>1281</v>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>TPM-0627</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>12-A-6200-03</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>P0-2603-2838</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>INT-031</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>Proyecto META</t>
+        </is>
+      </c>
+      <c r="H1234" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="n">
+        <v>1282</v>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>TPM-0628</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>17-D-6004-01</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1235" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="n">
+        <v>1283</v>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>TPM-0628</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>17-D-6004-02</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1236" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="n">
+        <v>1284</v>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>TPM-0628</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>PP1510-02</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1237" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="n">
+        <v>1285</v>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>TPM-0629</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>P6298-051</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1238" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="n">
+        <v>1286</v>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>TPM-0630</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>12-D-6348-12</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1239" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="n">
+        <v>1287</v>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>TPM-0631</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>12-D-6348-12</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1240" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="n">
+        <v>1288</v>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>TPM-0632</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>17-D-6025-04</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1241" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="n">
+        <v>1289</v>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>TPM-0632</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>17-D-6007-01</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>PO 2602-0711</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>INT-003</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>Entrega_P2</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>Proyecto RENO 6</t>
+        </is>
+      </c>
+      <c r="H1242" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="n">
+        <v>1290</v>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>TPM-0633</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>11-B-9211-01</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1243" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="n">
+        <v>1291</v>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>TPM-0633</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>11-A-9845-01</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1244" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="n">
+        <v>1292</v>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>TPM-0633</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>11-A-9847-01</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1245" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="n">
+        <v>1293</v>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>TPM-0633</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>11-B-9208-01 TRTO</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="n">
+        <v>1294</v>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>TPM-0633</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>11-B-9208-02 TRTO</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1247" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="n">
+        <v>1295</v>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>TPM-0633</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>11-D-9534-01 TRTO</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1248" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="n">
+        <v>1296</v>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>TPM-0633</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>11-D-9535-01 TRTO</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1249" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="n">
+        <v>1297</v>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>TPM-0634</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>11-E-9897-01</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1250" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="n">
+        <v>1298</v>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>TPM-0634</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>11-E-9897-03</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1251" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="n">
+        <v>1299</v>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>TPM-0634</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>11-E-9898-01</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1252" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="n">
+        <v>1300</v>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>TPM-0634</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>11-C-9245-01</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1253" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="n">
+        <v>1301</v>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>TPM-0634</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>11-C-9249-01</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1254" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="n">
+        <v>1302</v>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>TPM-0634</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>11-C-9250-01</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1255" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="n">
+        <v>1303</v>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>TPM-0634</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>11-E-9898-03</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1256" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="n">
+        <v>1304</v>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>TPM-0634</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>11-D-9978-202 TRTO</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1257" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="n">
+        <v>1305</v>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>TPM-0634</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>11-E-9675-01</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1258" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="n">
+        <v>1306</v>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>TPM-0634</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>11-E-9676-01</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1259" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Detalle_Tarimas.xlsx
+++ b/BD_Detalle_Tarimas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1259"/>
+  <dimension ref="A1:H1262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48262,6 +48262,120 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1260">
+      <c r="A1260" t="n">
+        <v>1307</v>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>TPM-0635</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>11-A-9843-01</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1260" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="n">
+        <v>1308</v>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>TPM-0635</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>11-B-9743-01</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1261" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="n">
+        <v>1309</v>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>TPM-0635</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>11-B-9743-02</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>PO 2608-3358</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>INT-057</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>Entrega_P1</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>Proyecto TORONTO DEC</t>
+        </is>
+      </c>
+      <c r="H1262" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
